--- a/fuzzy_tsukamoto-1 - Copy.xlsx
+++ b/fuzzy_tsukamoto-1 - Copy.xlsx
@@ -5,20 +5,21 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\puanm\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\tsukamoto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6783CF5F-E63B-4F7E-B072-629CEB26E1E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2680CE8-9161-4B95-9D82-2E76AE3188C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="parameter_fuzzy" sheetId="1" r:id="rId1"/>
-    <sheet name="aturan_fuzzy (rule)" sheetId="2" r:id="rId2"/>
-    <sheet name="data_input" sheetId="3" r:id="rId3"/>
-    <sheet name="fuzzifikasi" sheetId="4" r:id="rId4"/>
-    <sheet name="rule_evaluation (inferensi)" sheetId="7" r:id="rId5"/>
-    <sheet name="hasil_final (defuzzifikasi)" sheetId="8" r:id="rId6"/>
+    <sheet name="parameter_variabel_output" sheetId="9" r:id="rId2"/>
+    <sheet name="aturan_fuzzy (rule)" sheetId="2" r:id="rId3"/>
+    <sheet name="data_input" sheetId="3" r:id="rId4"/>
+    <sheet name="fuzzifikasi" sheetId="4" r:id="rId5"/>
+    <sheet name="rule_evaluation (inferensi)" sheetId="7" r:id="rId6"/>
+    <sheet name="hasil_final (defuzzifikasi)" sheetId="8" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="692" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="707" uniqueCount="88">
   <si>
     <t>Variabel</t>
   </si>
@@ -264,13 +265,52 @@
   </si>
   <si>
     <t>Selisih</t>
+  </si>
+  <si>
+    <t>Domain (Nilai)</t>
+  </si>
+  <si>
+    <t>Keterangan</t>
+  </si>
+  <si>
+    <t>Risiko</t>
+  </si>
+  <si>
+    <t>High Risk</t>
+  </si>
+  <si>
+    <t>0 - 40</t>
+  </si>
+  <si>
+    <t>Grafik Turun</t>
+  </si>
+  <si>
+    <t>Medium Risk</t>
+  </si>
+  <si>
+    <t>40 - 70</t>
+  </si>
+  <si>
+    <t>Grafik Segitiga</t>
+  </si>
+  <si>
+    <t>Low Risk</t>
+  </si>
+  <si>
+    <t>70 - 100</t>
+  </si>
+  <si>
+    <t>Grafik Naik</t>
+  </si>
+  <si>
+    <t>d</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -281,6 +321,12 @@
     <font>
       <sz val="11"/>
       <color rgb="FF1F1F1F"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -306,12 +352,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -614,16 +666,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" customWidth="1"/>
     <col min="3" max="3" width="10.88671875" customWidth="1"/>
     <col min="4" max="4" width="10.109375" customWidth="1"/>
     <col min="5" max="5" width="10.88671875" customWidth="1"/>
+    <col min="6" max="6" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -639,8 +692,11 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -651,13 +707,16 @@
         <v>0</v>
       </c>
       <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
         <v>30</v>
       </c>
-      <c r="E2">
+      <c r="F2">
         <v>60</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -668,13 +727,16 @@
         <v>30</v>
       </c>
       <c r="D3">
+        <v>60</v>
+      </c>
+      <c r="E3">
         <v>90</v>
       </c>
-      <c r="E3">
+      <c r="F3">
         <v>120</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -690,8 +752,11 @@
       <c r="E4">
         <v>300</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F4">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -702,13 +767,16 @@
         <v>0</v>
       </c>
       <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
         <v>25000000</v>
       </c>
-      <c r="E5">
+      <c r="F5">
         <v>50000000</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -719,13 +787,16 @@
         <v>30000000</v>
       </c>
       <c r="D6">
+        <v>60000000</v>
+      </c>
+      <c r="E6">
         <v>90000000</v>
       </c>
-      <c r="E6">
+      <c r="F6">
         <v>120000000</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -741,8 +812,11 @@
       <c r="E7">
         <v>300000000</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F7">
+        <v>300000000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -753,13 +827,16 @@
         <v>0</v>
       </c>
       <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
         <v>5000</v>
       </c>
-      <c r="E8">
+      <c r="F8">
         <v>10000</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -770,13 +847,16 @@
         <v>6000</v>
       </c>
       <c r="D9">
+        <v>10000</v>
+      </c>
+      <c r="E9">
         <v>15000</v>
       </c>
-      <c r="E9">
+      <c r="F9">
         <v>20000</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -790,6 +870,9 @@
         <v>25000</v>
       </c>
       <c r="E10">
+        <v>40000</v>
+      </c>
+      <c r="F10">
         <v>40000</v>
       </c>
     </row>
@@ -799,6 +882,75 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{982EA76B-4B17-459D-9940-DF16A1C623DF}">
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="10.109375" customWidth="1"/>
+    <col min="2" max="2" width="11.77734375" customWidth="1"/>
+    <col min="3" max="3" width="14.6640625" customWidth="1"/>
+    <col min="4" max="4" width="12.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="4"/>
+      <c r="B3" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="4"/>
+      <c r="B4" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1292,7 +1444,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1403,7 +1555,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1781,7 +1933,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{777D6FD5-F2D0-4C44-AC6E-04AA38328888}">
   <dimension ref="A1:I168"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -7494,7 +7646,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93AFB6DD-D566-44D3-A7C7-E886E510ABD2}">
   <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>

--- a/fuzzy_tsukamoto-1 - Copy.xlsx
+++ b/fuzzy_tsukamoto-1 - Copy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\tsukamoto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2680CE8-9161-4B95-9D82-2E76AE3188C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2C65530-6C46-4AFB-BF4B-B91FDD108A76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="parameter_fuzzy" sheetId="1" r:id="rId1"/>
@@ -288,22 +288,22 @@
     <t>Medium Risk</t>
   </si>
   <si>
-    <t>40 - 70</t>
-  </si>
-  <si>
     <t>Grafik Segitiga</t>
   </si>
   <si>
     <t>Low Risk</t>
   </si>
   <si>
-    <t>70 - 100</t>
-  </si>
-  <si>
     <t>Grafik Naik</t>
   </si>
   <si>
     <t>d</t>
+  </si>
+  <si>
+    <t>30 - 70</t>
+  </si>
+  <si>
+    <t>60 - 100</t>
   </si>
 </sst>
 </file>
@@ -693,7 +693,7 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -926,22 +926,22 @@
         <v>81</v>
       </c>
       <c r="C3" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>82</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4"/>
       <c r="B4" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>84</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -1998,8 +1998,8 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <f>IF(C2="Low_Risk", 70+(G2*30), IF(C2="Medium_Risk", 40+(G2*30), 40-(G2*40)))</f>
-        <v>40</v>
+        <f>IF(C2="Low_Risk", 60+(G2*40), IF(C2="Medium_Risk", 30+(G2*40), 40-(G2*40)))</f>
+        <v>30</v>
       </c>
       <c r="I2">
         <f>G2*H2</f>
@@ -2033,8 +2033,8 @@
         <v>0</v>
       </c>
       <c r="H3">
-        <f t="shared" ref="H3:H66" si="1">IF(C3="Low_Risk", 70+(G3*30), IF(C3="Medium_Risk", 40+(G3*30), 40-(G3*40)))</f>
-        <v>40</v>
+        <f t="shared" ref="H3:H66" si="1">IF(C3="Low_Risk", 60+(G3*40), IF(C3="Medium_Risk", 30+(G3*40), 40-(G3*40)))</f>
+        <v>30</v>
       </c>
       <c r="I3">
         <f t="shared" ref="I3:I66" si="2">G3*H3</f>
@@ -2069,7 +2069,7 @@
       </c>
       <c r="H4">
         <f t="shared" si="1"/>
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="I4">
         <f t="shared" si="2"/>
@@ -2104,7 +2104,7 @@
       </c>
       <c r="H5">
         <f t="shared" si="1"/>
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I5">
         <f t="shared" si="2"/>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="H6">
         <f t="shared" si="1"/>
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="I6">
         <f t="shared" si="2"/>
@@ -2174,7 +2174,7 @@
       </c>
       <c r="H7">
         <f t="shared" si="1"/>
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="I7">
         <f t="shared" si="2"/>
@@ -2209,7 +2209,7 @@
       </c>
       <c r="H8">
         <f t="shared" si="1"/>
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="I8">
         <f t="shared" si="2"/>
@@ -2244,7 +2244,7 @@
       </c>
       <c r="H9">
         <f t="shared" si="1"/>
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="I9">
         <f t="shared" si="2"/>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="H10">
         <f t="shared" si="1"/>
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="I10">
         <f t="shared" si="2"/>
@@ -2349,7 +2349,7 @@
       </c>
       <c r="H12">
         <f t="shared" si="1"/>
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I12">
         <f t="shared" si="2"/>
@@ -2384,7 +2384,7 @@
       </c>
       <c r="H13">
         <f t="shared" si="1"/>
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I13">
         <f t="shared" si="2"/>
@@ -2419,7 +2419,7 @@
       </c>
       <c r="H14">
         <f t="shared" si="1"/>
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I14">
         <f t="shared" si="2"/>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="H15">
         <f t="shared" si="1"/>
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I15">
         <f t="shared" si="2"/>
@@ -2489,7 +2489,7 @@
       </c>
       <c r="H16">
         <f t="shared" si="1"/>
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="I16">
         <f t="shared" si="2"/>
@@ -2524,7 +2524,7 @@
       </c>
       <c r="H17">
         <f t="shared" si="1"/>
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I17">
         <f t="shared" si="2"/>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="H18">
         <f t="shared" si="1"/>
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="I18">
         <f t="shared" si="2"/>
@@ -2594,11 +2594,11 @@
       </c>
       <c r="H19">
         <f t="shared" si="1"/>
-        <v>90</v>
+        <v>86.666666666666657</v>
       </c>
       <c r="I19">
         <f t="shared" si="2"/>
-        <v>60</v>
+        <v>57.777777777777771</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
@@ -2699,7 +2699,7 @@
       </c>
       <c r="H22">
         <f t="shared" si="1"/>
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I22">
         <f t="shared" si="2"/>
@@ -2769,7 +2769,7 @@
       </c>
       <c r="H24">
         <f t="shared" si="1"/>
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I24">
         <f t="shared" si="2"/>
@@ -2804,7 +2804,7 @@
       </c>
       <c r="H25">
         <f t="shared" si="1"/>
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I25">
         <f t="shared" si="2"/>
@@ -2839,7 +2839,7 @@
       </c>
       <c r="H26">
         <f t="shared" si="1"/>
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I26">
         <f t="shared" si="2"/>
@@ -2874,7 +2874,7 @@
       </c>
       <c r="H27">
         <f t="shared" si="1"/>
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I27">
         <f t="shared" si="2"/>
@@ -2909,11 +2909,11 @@
       </c>
       <c r="H28">
         <f t="shared" si="1"/>
-        <v>75</v>
+        <v>66.666666666666671</v>
       </c>
       <c r="I28">
         <f t="shared" si="2"/>
-        <v>12.5</v>
+        <v>11.111111111111111</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="H30">
         <f t="shared" si="1"/>
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I30">
         <f t="shared" si="2"/>
@@ -2979,7 +2979,7 @@
       </c>
       <c r="H31">
         <f t="shared" si="1"/>
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I31">
         <f t="shared" si="2"/>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="H32">
         <f t="shared" si="1"/>
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="I32">
         <f t="shared" si="2"/>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="H33">
         <f t="shared" si="1"/>
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I33">
         <f t="shared" si="2"/>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="H34">
         <f t="shared" si="1"/>
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="I34">
         <f t="shared" si="2"/>
@@ -3119,7 +3119,7 @@
       </c>
       <c r="H35">
         <f t="shared" si="1"/>
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="I35">
         <f t="shared" si="2"/>
@@ -3154,7 +3154,7 @@
       </c>
       <c r="H36">
         <f t="shared" si="1"/>
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="I36">
         <f t="shared" si="2"/>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="H37">
         <f t="shared" si="1"/>
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="I37">
         <f t="shared" si="2"/>
@@ -3294,7 +3294,7 @@
       </c>
       <c r="H40">
         <f t="shared" si="1"/>
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I40">
         <f t="shared" si="2"/>
@@ -3329,7 +3329,7 @@
       </c>
       <c r="H41">
         <f t="shared" si="1"/>
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I41">
         <f t="shared" si="2"/>
@@ -3364,7 +3364,7 @@
       </c>
       <c r="H42">
         <f t="shared" si="1"/>
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I42">
         <f t="shared" si="2"/>
@@ -3399,7 +3399,7 @@
       </c>
       <c r="H43">
         <f t="shared" si="1"/>
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I43">
         <f t="shared" si="2"/>
@@ -3434,7 +3434,7 @@
       </c>
       <c r="H44">
         <f t="shared" si="1"/>
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="I44">
         <f t="shared" si="2"/>
@@ -3469,7 +3469,7 @@
       </c>
       <c r="H45">
         <f t="shared" si="1"/>
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I45">
         <f t="shared" si="2"/>
@@ -3504,7 +3504,7 @@
       </c>
       <c r="H46">
         <f t="shared" si="1"/>
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="I46">
         <f t="shared" si="2"/>
@@ -3539,7 +3539,7 @@
       </c>
       <c r="H47">
         <f t="shared" si="1"/>
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="I47">
         <f t="shared" si="2"/>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="H50">
         <f t="shared" si="1"/>
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I50">
         <f t="shared" si="2"/>
@@ -3714,7 +3714,7 @@
       </c>
       <c r="H52">
         <f t="shared" si="1"/>
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I52">
         <f t="shared" si="2"/>
@@ -3749,7 +3749,7 @@
       </c>
       <c r="H53">
         <f t="shared" si="1"/>
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I53">
         <f t="shared" si="2"/>
@@ -3784,7 +3784,7 @@
       </c>
       <c r="H54">
         <f t="shared" si="1"/>
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I54">
         <f t="shared" si="2"/>
@@ -3819,7 +3819,7 @@
       </c>
       <c r="H55">
         <f t="shared" si="1"/>
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I55">
         <f t="shared" si="2"/>
@@ -3854,7 +3854,7 @@
       </c>
       <c r="H56">
         <f t="shared" si="1"/>
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="I56">
         <f t="shared" si="2"/>
@@ -3889,7 +3889,7 @@
       </c>
       <c r="H58">
         <f t="shared" si="1"/>
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I58">
         <f t="shared" si="2"/>
@@ -3924,11 +3924,11 @@
       </c>
       <c r="H59">
         <f t="shared" si="1"/>
-        <v>44.753320000000002</v>
+        <v>36.337760000000003</v>
       </c>
       <c r="I59">
         <f t="shared" si="2"/>
-        <v>7.0908950340800008</v>
+        <v>5.7575000454400005</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.3">
@@ -3959,7 +3959,7 @@
       </c>
       <c r="H60">
         <f t="shared" si="1"/>
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="I60">
         <f t="shared" si="2"/>
@@ -3994,7 +3994,7 @@
       </c>
       <c r="H61">
         <f t="shared" si="1"/>
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I61">
         <f t="shared" si="2"/>
@@ -4029,11 +4029,11 @@
       </c>
       <c r="H62">
         <f t="shared" si="1"/>
-        <v>86.038899999999998</v>
+        <v>81.385199999999998</v>
       </c>
       <c r="I62">
         <f t="shared" si="2"/>
-        <v>45.998977107000002</v>
+        <v>43.510969476</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.3">
@@ -4064,7 +4064,7 @@
       </c>
       <c r="H63">
         <f t="shared" si="1"/>
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="I63">
         <f t="shared" si="2"/>
@@ -4099,7 +4099,7 @@
       </c>
       <c r="H64">
         <f t="shared" si="1"/>
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="I64">
         <f t="shared" si="2"/>
@@ -4134,7 +4134,7 @@
       </c>
       <c r="H65">
         <f t="shared" si="1"/>
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="I65">
         <f t="shared" si="2"/>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="H66">
         <f t="shared" si="1"/>
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="I66">
         <f t="shared" si="2"/>
@@ -4203,7 +4203,7 @@
         <v>0</v>
       </c>
       <c r="H67">
-        <f t="shared" ref="H67:H130" si="4">IF(C67="Low_Risk", 70+(G67*30), IF(C67="Medium_Risk", 40+(G67*30), 40-(G67*40)))</f>
+        <f t="shared" ref="H67:H130" si="4">IF(C67="Low_Risk", 60+(G67*40), IF(C67="Medium_Risk", 30+(G67*40), 40-(G67*40)))</f>
         <v>40</v>
       </c>
       <c r="I67">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="H68">
         <f t="shared" si="4"/>
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I68">
         <f t="shared" si="5"/>
@@ -4274,7 +4274,7 @@
       </c>
       <c r="H69">
         <f t="shared" si="4"/>
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I69">
         <f t="shared" si="5"/>
@@ -4309,7 +4309,7 @@
       </c>
       <c r="H70">
         <f t="shared" si="4"/>
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I70">
         <f t="shared" si="5"/>
@@ -4344,7 +4344,7 @@
       </c>
       <c r="H71">
         <f t="shared" si="4"/>
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I71">
         <f t="shared" si="5"/>
@@ -4379,7 +4379,7 @@
       </c>
       <c r="H72">
         <f t="shared" si="4"/>
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="I72">
         <f t="shared" si="5"/>
@@ -4414,7 +4414,7 @@
       </c>
       <c r="H73">
         <f t="shared" si="4"/>
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I73">
         <f t="shared" si="5"/>
@@ -4449,7 +4449,7 @@
       </c>
       <c r="H74">
         <f t="shared" si="4"/>
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="I74">
         <f t="shared" si="5"/>
@@ -4484,7 +4484,7 @@
       </c>
       <c r="H75">
         <f t="shared" si="4"/>
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="I75">
         <f t="shared" si="5"/>
@@ -4589,7 +4589,7 @@
       </c>
       <c r="H78">
         <f t="shared" si="4"/>
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I78">
         <f t="shared" si="5"/>
@@ -4659,7 +4659,7 @@
       </c>
       <c r="H80">
         <f t="shared" si="4"/>
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I80">
         <f t="shared" si="5"/>
@@ -4694,7 +4694,7 @@
       </c>
       <c r="H81">
         <f t="shared" si="4"/>
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I81">
         <f t="shared" si="5"/>
@@ -4729,7 +4729,7 @@
       </c>
       <c r="H82">
         <f t="shared" si="4"/>
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I82">
         <f t="shared" si="5"/>
@@ -4764,7 +4764,7 @@
       </c>
       <c r="H83">
         <f t="shared" si="4"/>
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I83">
         <f t="shared" si="5"/>
@@ -4799,7 +4799,7 @@
       </c>
       <c r="H84">
         <f t="shared" si="4"/>
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="I84">
         <f t="shared" si="5"/>
@@ -4834,7 +4834,7 @@
       </c>
       <c r="H86">
         <f t="shared" si="4"/>
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I86">
         <f t="shared" si="5"/>
@@ -4869,7 +4869,7 @@
       </c>
       <c r="H87">
         <f t="shared" si="4"/>
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I87">
         <f t="shared" si="5"/>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="H88">
         <f t="shared" si="4"/>
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="I88">
         <f t="shared" si="5"/>
@@ -4939,11 +4939,11 @@
       </c>
       <c r="H89">
         <f t="shared" si="4"/>
-        <v>44.613999999999997</v>
+        <v>36.152000000000001</v>
       </c>
       <c r="I89">
         <f t="shared" si="5"/>
-        <v>6.8616331999999991</v>
+        <v>5.5601776000000003</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.3">
@@ -4974,11 +4974,11 @@
       </c>
       <c r="H90">
         <f t="shared" si="4"/>
-        <v>90.951999999999998</v>
+        <v>87.936000000000007</v>
       </c>
       <c r="I90">
         <f t="shared" si="5"/>
-        <v>63.520876800000003</v>
+        <v>61.414502400000003</v>
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.3">
@@ -5009,7 +5009,7 @@
       </c>
       <c r="H91">
         <f t="shared" si="4"/>
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="I91">
         <f t="shared" si="5"/>
@@ -5044,7 +5044,7 @@
       </c>
       <c r="H92">
         <f t="shared" si="4"/>
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="I92">
         <f t="shared" si="5"/>
@@ -5079,7 +5079,7 @@
       </c>
       <c r="H93">
         <f t="shared" si="4"/>
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="I93">
         <f t="shared" si="5"/>
@@ -5114,7 +5114,7 @@
       </c>
       <c r="H94">
         <f t="shared" si="4"/>
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="I94">
         <f t="shared" si="5"/>
@@ -5184,7 +5184,7 @@
       </c>
       <c r="H96">
         <f t="shared" si="4"/>
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I96">
         <f t="shared" si="5"/>
@@ -5219,7 +5219,7 @@
       </c>
       <c r="H97">
         <f t="shared" si="4"/>
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I97">
         <f t="shared" si="5"/>
@@ -5254,11 +5254,11 @@
       </c>
       <c r="H98">
         <f t="shared" si="4"/>
-        <v>44.613999999999997</v>
+        <v>36.152000000000001</v>
       </c>
       <c r="I98">
         <f t="shared" si="5"/>
-        <v>6.8616331999999991</v>
+        <v>5.5601776000000003</v>
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.3">
@@ -5289,11 +5289,11 @@
       </c>
       <c r="H99">
         <f t="shared" si="4"/>
-        <v>45</v>
+        <v>36.666666666666664</v>
       </c>
       <c r="I99">
         <f t="shared" si="5"/>
-        <v>7.5</v>
+        <v>6.1111111111111107</v>
       </c>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.3">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="H100">
         <f t="shared" si="4"/>
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="I100">
         <f t="shared" si="5"/>
@@ -5359,7 +5359,7 @@
       </c>
       <c r="H101">
         <f t="shared" si="4"/>
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I101">
         <f t="shared" si="5"/>
@@ -5394,7 +5394,7 @@
       </c>
       <c r="H102">
         <f t="shared" si="4"/>
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="I102">
         <f t="shared" si="5"/>
@@ -5429,7 +5429,7 @@
       </c>
       <c r="H103">
         <f t="shared" si="4"/>
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="I103">
         <f t="shared" si="5"/>
@@ -5534,7 +5534,7 @@
       </c>
       <c r="H106">
         <f t="shared" si="4"/>
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I106">
         <f t="shared" si="5"/>
@@ -5604,7 +5604,7 @@
       </c>
       <c r="H108">
         <f t="shared" si="4"/>
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I108">
         <f t="shared" si="5"/>
@@ -5639,7 +5639,7 @@
       </c>
       <c r="H109">
         <f t="shared" si="4"/>
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I109">
         <f t="shared" si="5"/>
@@ -5674,7 +5674,7 @@
       </c>
       <c r="H110">
         <f t="shared" si="4"/>
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I110">
         <f t="shared" si="5"/>
@@ -5709,7 +5709,7 @@
       </c>
       <c r="H111">
         <f t="shared" si="4"/>
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I111">
         <f t="shared" si="5"/>
@@ -5744,7 +5744,7 @@
       </c>
       <c r="H112">
         <f t="shared" si="4"/>
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="I112">
         <f t="shared" si="5"/>
@@ -5779,7 +5779,7 @@
       </c>
       <c r="H114">
         <f t="shared" si="4"/>
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I114">
         <f t="shared" si="5"/>
@@ -5814,7 +5814,7 @@
       </c>
       <c r="H115">
         <f t="shared" si="4"/>
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I115">
         <f t="shared" si="5"/>
@@ -5849,7 +5849,7 @@
       </c>
       <c r="H116">
         <f t="shared" si="4"/>
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="I116">
         <f t="shared" si="5"/>
@@ -5884,11 +5884,11 @@
       </c>
       <c r="H117">
         <f t="shared" si="4"/>
-        <v>43.45</v>
+        <v>34.6</v>
       </c>
       <c r="I117">
         <f t="shared" si="5"/>
-        <v>4.9967500000000005</v>
+        <v>3.9790000000000005</v>
       </c>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.3">
@@ -5919,11 +5919,11 @@
       </c>
       <c r="H118">
         <f t="shared" si="4"/>
-        <v>80</v>
+        <v>73.333333333333329</v>
       </c>
       <c r="I118">
         <f t="shared" si="5"/>
-        <v>26.666666666666664</v>
+        <v>24.444444444444443</v>
       </c>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.3">
@@ -5954,7 +5954,7 @@
       </c>
       <c r="H119">
         <f t="shared" si="4"/>
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="I119">
         <f t="shared" si="5"/>
@@ -5989,7 +5989,7 @@
       </c>
       <c r="H120">
         <f t="shared" si="4"/>
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="I120">
         <f t="shared" si="5"/>
@@ -6024,7 +6024,7 @@
       </c>
       <c r="H121">
         <f t="shared" si="4"/>
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="I121">
         <f t="shared" si="5"/>
@@ -6059,7 +6059,7 @@
       </c>
       <c r="H122">
         <f t="shared" si="4"/>
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="I122">
         <f t="shared" si="5"/>
@@ -6129,7 +6129,7 @@
       </c>
       <c r="H124">
         <f t="shared" si="4"/>
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I124">
         <f t="shared" si="5"/>
@@ -6164,7 +6164,7 @@
       </c>
       <c r="H125">
         <f t="shared" si="4"/>
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I125">
         <f t="shared" si="5"/>
@@ -6199,11 +6199,11 @@
       </c>
       <c r="H126">
         <f t="shared" si="4"/>
-        <v>43.45</v>
+        <v>34.6</v>
       </c>
       <c r="I126">
         <f t="shared" si="5"/>
-        <v>4.9967500000000005</v>
+        <v>3.9790000000000005</v>
       </c>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.3">
@@ -6234,11 +6234,11 @@
       </c>
       <c r="H127">
         <f t="shared" si="4"/>
-        <v>60</v>
+        <v>56.666666666666664</v>
       </c>
       <c r="I127">
         <f t="shared" si="5"/>
-        <v>40</v>
+        <v>37.777777777777771</v>
       </c>
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.3">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="H128">
         <f t="shared" si="4"/>
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="I128">
         <f t="shared" si="5"/>
@@ -6304,7 +6304,7 @@
       </c>
       <c r="H129">
         <f t="shared" si="4"/>
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I129">
         <f t="shared" si="5"/>
@@ -6339,7 +6339,7 @@
       </c>
       <c r="H130">
         <f t="shared" si="4"/>
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="I130">
         <f t="shared" si="5"/>
@@ -6373,8 +6373,8 @@
         <v>0</v>
       </c>
       <c r="H131">
-        <f t="shared" ref="H131:H168" si="7">IF(C131="Low_Risk", 70+(G131*30), IF(C131="Medium_Risk", 40+(G131*30), 40-(G131*40)))</f>
-        <v>70</v>
+        <f t="shared" ref="H131:H168" si="7">IF(C131="Low_Risk", 60+(G131*40), IF(C131="Medium_Risk", 30+(G131*40), 40-(G131*40)))</f>
+        <v>60</v>
       </c>
       <c r="I131">
         <f t="shared" ref="I131:I168" si="8">G131*H131</f>
@@ -6479,7 +6479,7 @@
       </c>
       <c r="H134">
         <f t="shared" si="7"/>
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I134">
         <f t="shared" si="8"/>
@@ -6549,7 +6549,7 @@
       </c>
       <c r="H136">
         <f t="shared" si="7"/>
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I136">
         <f t="shared" si="8"/>
@@ -6584,7 +6584,7 @@
       </c>
       <c r="H137">
         <f t="shared" si="7"/>
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I137">
         <f t="shared" si="8"/>
@@ -6619,7 +6619,7 @@
       </c>
       <c r="H138">
         <f t="shared" si="7"/>
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I138">
         <f t="shared" si="8"/>
@@ -6654,7 +6654,7 @@
       </c>
       <c r="H139">
         <f t="shared" si="7"/>
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I139">
         <f t="shared" si="8"/>
@@ -6689,11 +6689,17 @@
       </c>
       <c r="H140">
         <f t="shared" si="7"/>
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="I140">
         <f t="shared" si="8"/>
         <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H141">
+        <f t="shared" si="7"/>
+        <v>40</v>
       </c>
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.3">
@@ -6724,7 +6730,7 @@
       </c>
       <c r="H142">
         <f t="shared" si="7"/>
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I142">
         <f t="shared" si="8"/>
@@ -6759,7 +6765,7 @@
       </c>
       <c r="H143">
         <f t="shared" si="7"/>
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I143">
         <f t="shared" si="8"/>
@@ -6794,7 +6800,7 @@
       </c>
       <c r="H144">
         <f t="shared" si="7"/>
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="I144">
         <f t="shared" si="8"/>
@@ -6829,7 +6835,7 @@
       </c>
       <c r="H145">
         <f t="shared" si="7"/>
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I145">
         <f t="shared" si="8"/>
@@ -6864,7 +6870,7 @@
       </c>
       <c r="H146">
         <f t="shared" si="7"/>
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="I146">
         <f t="shared" si="8"/>
@@ -6899,7 +6905,7 @@
       </c>
       <c r="H147">
         <f t="shared" si="7"/>
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="I147">
         <f t="shared" si="8"/>
@@ -6934,7 +6940,7 @@
       </c>
       <c r="H148">
         <f t="shared" si="7"/>
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="I148">
         <f t="shared" si="8"/>
@@ -6969,7 +6975,7 @@
       </c>
       <c r="H149">
         <f t="shared" si="7"/>
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="I149">
         <f t="shared" si="8"/>
@@ -7004,7 +7010,7 @@
       </c>
       <c r="H150">
         <f t="shared" si="7"/>
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="I150">
         <f t="shared" si="8"/>
@@ -7074,7 +7080,7 @@
       </c>
       <c r="H152">
         <f t="shared" si="7"/>
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I152">
         <f t="shared" si="8"/>
@@ -7109,7 +7115,7 @@
       </c>
       <c r="H153">
         <f t="shared" si="7"/>
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I153">
         <f t="shared" si="8"/>
@@ -7144,7 +7150,7 @@
       </c>
       <c r="H154">
         <f t="shared" si="7"/>
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I154">
         <f t="shared" si="8"/>
@@ -7179,7 +7185,7 @@
       </c>
       <c r="H155">
         <f t="shared" si="7"/>
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I155">
         <f t="shared" si="8"/>
@@ -7214,7 +7220,7 @@
       </c>
       <c r="H156">
         <f t="shared" si="7"/>
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="I156">
         <f t="shared" si="8"/>
@@ -7249,7 +7255,7 @@
       </c>
       <c r="H157">
         <f t="shared" si="7"/>
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I157">
         <f t="shared" si="8"/>
@@ -7284,7 +7290,7 @@
       </c>
       <c r="H158">
         <f t="shared" si="7"/>
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="I158">
         <f t="shared" si="8"/>
@@ -7319,7 +7325,7 @@
       </c>
       <c r="H159">
         <f t="shared" si="7"/>
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="I159">
         <f t="shared" si="8"/>
@@ -7424,7 +7430,7 @@
       </c>
       <c r="H162">
         <f t="shared" si="7"/>
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I162">
         <f t="shared" si="8"/>
@@ -7494,7 +7500,7 @@
       </c>
       <c r="H164">
         <f t="shared" si="7"/>
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I164">
         <f t="shared" si="8"/>
@@ -7529,7 +7535,7 @@
       </c>
       <c r="H165">
         <f t="shared" si="7"/>
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I165">
         <f t="shared" si="8"/>
@@ -7564,7 +7570,7 @@
       </c>
       <c r="H166">
         <f t="shared" si="7"/>
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I166">
         <f t="shared" si="8"/>
@@ -7599,7 +7605,7 @@
       </c>
       <c r="H167">
         <f t="shared" si="7"/>
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I167">
         <f t="shared" si="8"/>
@@ -7634,7 +7640,7 @@
       </c>
       <c r="H168">
         <f t="shared" si="7"/>
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="I168">
         <f t="shared" si="8"/>
@@ -7684,11 +7690,11 @@
       </c>
       <c r="C2">
         <f>SUMIF('rule_evaluation (inferensi)'!A:A, A2, 'rule_evaluation (inferensi)'!I:I)</f>
-        <v>72.5</v>
+        <v>68.888888888888886</v>
       </c>
       <c r="D2">
         <f>IF(B2=0, 0, C2/B2)</f>
-        <v>87.000000000000014</v>
+        <v>82.666666666666671</v>
       </c>
       <c r="E2" t="str">
         <f>IF(D2&gt;=70, "Low Risk", IF(D2&gt;=40, "Medium Risk", "High Risk"))</f>
@@ -7726,11 +7732,11 @@
       </c>
       <c r="C4">
         <f>SUMIF('rule_evaluation (inferensi)'!A:A, A4, 'rule_evaluation (inferensi)'!I:I)</f>
-        <v>76.660166666666669</v>
+        <v>70.180222222222213</v>
       </c>
       <c r="D4">
         <f t="shared" si="0"/>
-        <v>62.325338753387534</v>
+        <v>57.057091237579037</v>
       </c>
       <c r="E4" t="str">
         <f t="shared" si="1"/>
@@ -7747,11 +7753,11 @@
       </c>
       <c r="C5">
         <f>SUMIF('rule_evaluation (inferensi)'!A:A, A5, 'rule_evaluation (inferensi)'!I:I)</f>
-        <v>53.089872141080001</v>
+        <v>49.268469521439997</v>
       </c>
       <c r="D5">
         <f t="shared" si="0"/>
-        <v>76.600582536756534</v>
+        <v>71.086881806906604</v>
       </c>
       <c r="E5" t="str">
         <f t="shared" si="1"/>
@@ -7768,15 +7774,15 @@
       </c>
       <c r="C6">
         <f>SUMIF('rule_evaluation (inferensi)'!A:A, A6, 'rule_evaluation (inferensi)'!I:I)</f>
-        <v>84.744143199999996</v>
+        <v>78.645968711111124</v>
       </c>
       <c r="D6">
         <f t="shared" si="0"/>
-        <v>72.266182376350187</v>
+        <v>67.065919878718972</v>
       </c>
       <c r="E6" t="str">
         <f t="shared" si="1"/>
-        <v>Low Risk</v>
+        <v>Medium Risk</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
